--- a/mapping/templates/GUIDE_Doppio/API_MMS200MI_ItemToolbox.xlsx
+++ b/mapping/templates/GUIDE_Doppio/API_MMS200MI_ItemToolbox.xlsx
@@ -184,126 +184,11 @@
 99: Item no longer stocked due to item number change. The item is only in the item file.</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Item number
-The field indicates the item number (for Maintenance, the item number or equipment number), which is a unique ID for an individual item.
-Items are entered and maintained in (MMS001). Item number can consist up to 15 alphanumeric characters.
-</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Name
-The field indicates the name for each item. The max allowed length of the item name can be controlled via (CRS735).
-</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Description
-The field indicates a supplementary description of the item. The maximum length of the item description can be controlled via (CRS735).
-The description information can be configured when 'Dynamic description' parameter is deactivated in (CRS760). The configurable description is set up in (MWS050) with number type 6 ('Item description'), and in (MWS051).
-The item numbering rule is linked to the item type and language via (MWS045). If it is activated, the item description will be built via item numbering rules. If no record is activated, the first 32 positions can be maintained in a separate field in the Work-with function for items (the I panel), displayed in a 3*10 format.
-The description can be used as a search key.
-</t>
-      </text>
-    </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">Item responsible
 The field indicates the user ID of the person responsible for the information found in the item file.
 </t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Basic unit of measure
-The field indicates the unit in which each item is recorded in inventory, even if alternate inventory units of measure are used. All balance information for the current item is always stored in this unit.
-</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Item group
-The field indicates the item group from which items should be included in the forecast adjustment.
-The information is used as selection and sorting criteria in different contexts.
-</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Product group
-The field indicates the product group from which items should be included in the forecast adjustment.
-The information is used as selection and sorting criteria in different contexts.
-</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Business area
-The field indicates the business area for this shop. This business area is a tool used to group information for budgeting and statistical purposes and is created in (CRS036).
-</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Item type
-The field indicates the item type, which determines an item's life cycle. The item type is mandatory and cannot be changed after the item is created. The only time an item type can be changed is when you copy template items.
-The functions connected to the item type include:
--A template item that contains default values for creating items.
--A numbering rule for assigning the correct item number based on settings in (MWS050).
--Field control in (MWS041) that sets the fields displayed for the item in (MMS001), the item/warehouse in (MMS002), and the item/facility in (MMS003).
--A warehouse/item type in (MWS042) to set the item/warehouse records generated when you create an item.
--An alias/item type in (MWS043) that is used to set the alias numbers generated when you create an item. Alias numbers are EAN13, UPC, popular numbers, and so on.
-The item type can also be used as selection criteria to find any type of item, such as raw material, purchased components, semi-finished products, and finished products. Item types are defined in (CRS040), where they can also be linked to an item category.
-</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Make/buy code
-The field indicates whether the item is manufactured in-house or purchased.
-1: Manufactured
-2: Purchased.</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Configuration code
-The field indicates if the item is configured when ordered or configured as a maintenance item.
-0: No.
-1: Yes.
-2: Yes, as a family item from which product variants with item numbers are created.
-3: No. The item is a product variant with the item number of the family item.
-4: The item is a maintenance item. Regulates the item costing.
-5: The item is a maintenance item. Possibility to answer inquiries to get a better planned work order.</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Inventory accounting
-The field indicates whether the stock kept for the item is accounted in inventory.
-0: No.
-1: Yes, the item is inventory accounted.
-2: No, the item is not inventory accounted, but it is planned as demand in the material planning process in (MMS080).
-3: No, the item is not inventory accounted, but it is planned as a function number. A function number is a dummy number for items that can replace each other. So material planning for the item is done on the function number level instead of the item level.</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t>Lot numbering method
-The field indicates how the serial number is created.
-0: Manually
-1: Automatically, using YYMM plus a sequence number
-2: Automatically, using YY plus a sequence number
-3: Automatically, using a sequence number
-4: Goods receiving number generated during goods receipt, but this must be entered manually
-5: Order number - only used with manufacturing orders
-6: Automatically, using YYMMDD plus a sequence number
-7: Automatically, using the numbering rules defined in (CRS040)
-8: Simple lot tracing for outbound deliveries, mandatory to fill in a lot reference when reporting picking lines
-9: Simple lot tracing for outbound deliveries, optional to fill in a lot reference when reporting picking list lines.</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
@@ -321,16 +206,6 @@
 </t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
-      <text>
-        <t>Inspection code
-The field indicates if and how the item should be quality inspected.
-0: The item should not be quality inspected.
-1: The item should be quality inspected but without a quality request.
-2: The item should be quality inspected together with a quality request.
-3: The item should be quality inspected together with a quality request and automatically create inspection records in (PPS300) and lots in (MMS235).</t>
-      </text>
-    </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>Lot control method
@@ -342,111 +217,12 @@
 5: Lot control used. All lots must be entered in the lot master. Serial number specification is connected to each lot.</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Purchase order U/M
-The field indicates the unit of measure (U/M) in which the quantity on the purchase order is expressed.
-The purchase order U/M can be the alternate U/M or the item's standard purchase U/M, if an alternate does not exist. If there is no standard purchase U/M, the item's basic U/M is used.
-</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t>Alternate U/M in use
-The field indicates if and how alternate units of measure can be used for an item.
-0: No alternate units of measurement can be used.
-1: Alternate units of measurement exist but must never differ from the standard U/M - purchase order, defined in(MMS015/E). This alternative applies to purchase orders only.
-2: Alternate units of measurement exist and are permitted, under the condition that the unit is entered for the item.</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t>Expiration date method
-The field indicates how the expiration date is calculated. This is used to set the expiration date, which is primarily used to obtain a correct priority date for lots in (MMS060). This, in turn, is used for automatic allocation when following FIFO principles.
-0: Expiration date missing. The receipt date is used as the priority date for allocation if lot control is used.
-1: The expiration date is calculated from the goods receiving/receipt date using the item's shelf life. This date can be overridden in goods receiving for purchasing and in receipt for manufacturing orders.
-2: The expiration date is calculated from the production date specified (either in goods receiving for purchasing or in receipt for manufacturing orders). This date can be overridden.
-3: The same as alternative 1, except that if the number of days is changed according to shelf life, re-inspection time or sales time it will update all warehouses for the item.
-4: The same as alternative 2, except that if the number of days is changed according to shelf life, re-inspection time or sales time it will update all warehouses for the item.</t>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Goods receiving method
-The field indicates the method that controls the processing of the goods receiving flow. Depending on the method, quality inspection may be performed, certain documents may be printed, etc.
-On the purchase order line, a default goods receiving method is proposed. This method may be overridden. The proposal is retrieved from one of three sources according to the following priority ranking:
-</t>
-      </text>
-    </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
-      <text>
-        <t>Sales item
-The field indicates if the item is a sales item.
-0: No, customer orders/service orders may not be entered.
-1: Yes, customer orders/service orders may be entered.
-2: Yes, but customer orders/service orders may only be entered if the item is a component in a KIT.</t>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Tax code
-The field indicates if an item, charge, customer or ship-to location is taxable or not.
-The tax code is used to calculate US sales tax.
-</t>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Attribute model
-The field indicates the ID of an attribute model.
-Attribute models are connected to items and used to set the attributes that can be connected to the item.
-</t>
-      </text>
-    </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
-      <text>
-        <t>Attribute managed
-The field indicates whether the item is processed using attribute management.
-0: No.
-1: Yes, the attribute panel is displayed automatically.
-2: Yes, the attribute panel is always displayed for receipt to stock. The panel is displayed for order entry only when an attribute value is incorrect.
-3: Yes, the attribute panel is only displayed when an attribute value is incorrect. This applies both to order entry and receipt to stock.</t>
-      </text>
-    </comment>
-    <comment ref="AB1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Number of decimal places
-The field indicates how many decimal places are to be used in connection with processing quantities.
-Zero to six decimal places may be used.
-</t>
-      </text>
-    </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
-      <text>
-        <t>Number of price decimal places
-The field indicates how many decimal places that should be used when displaying or entering prices.
-0: No decimals
-1: One
-2: Two
-3: Three
-4: Four</t>
-      </text>
-    </comment>
     <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">Commission group
 The field indicates the commission group, which is used to create bonus item matrices and bonus customer matrices. Commission groups are specified for each customer and item.
 These bonus matrices are used when creating bonus or commission agreements to identify the items and/or customers covered.
 </t>
-      </text>
-    </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
-      <text>
-        <t>Fixed or dynamic sales price U/M
-The field indicates if the sales price U/M is fixed or dynamic.
-0: Item is not a sales item
-1: Fixed
-2: Dynamic</t>
       </text>
     </comment>
   </commentList>
@@ -459,105 +235,11 @@
     <author>System</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Company
-The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.
-</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Warehouse
-The field indicates the warehouse ID.
-Warehouse is a stock zone which is used to distinguish different geographical locations within a company. The warehouse is used as a planning level for material and production. Stock zones, stock locations and items are connected to the warehouse.
-Warehouses are created in (MMS005).
-</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Item number
-The field indicates the item number (for Maintenance, the item number or equipment number), which is a unique ID for an individual item.
-Items are entered and maintained in (MMS001). Item number can consist up to 15 alphanumeric characters.
-</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Container management
-The field indicates how containers are managed. Container management is used to account for items in inventory using a container ID, such as a pallet number.
-0: Containers are not used.
-1: Containers are used. No verification that the container exists in the container master.
-2: Containers are used. Verification that the container exists in the container master.
-3: Containers are used. These must be defined as lot numbers. An existence check is performed against the lot master file.
-4: Same as method 1, but the container can only be stored in one location at a time.
-5: Same as method 2, but the container can only be stored in one location at a time.
-6: Same as method 3, but the container can only be stored in one location at a time.
-7: The container number indicates a package in stock (MMS470) and can only be stored in one location at a time.</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Allocation method
-The field indicates how allocation is carried out for each item/warehouse combination.
-1: Manual allocation.
-2: Automatic allocation using the allocation table if one is created for the item. If there is no table, allocation is done using FIFO without considering the location type.
-3: Automatic allocation for the location entered for each item/warehouse or the location specified for the order line (if one is specified). This allows the user to force allocation from a particular location. Overallocation is allowed for each location but not for each warehouse. This method cannot be used if the item is lot controlled.
-4: Automatic allocation for the location entered for each item/warehouse or the location specified for the order line (if one is specified). This allows the user to force allocation from a particular location. Allocation is done without a balance check. This method cannot be used if the item is lot controlled.
-5: Automatic allocation using the allocation table, and total required quantity must be allocatable on the same lot. This method can only be used in combination with lot control.
-6: Soft automatic allocation with a check against allocatable balance on warehouse level. See Note 1.
-7: Soft automatic allocation without balance check. See Note 1.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Storage method
-The field indicates the storage method for each item/warehouse, and determines how the item is distributed at different locations.
-1: Single location
-2: Multiple location
-3: Multiple location where reorder points are used.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Issue method
-The field indicates when and how material issues to work orders and manufacturing orders are reported.
-1: Material is issued against a picking list according to the allocation method used. Note that this method should be used if the item is order-initiated.
-2: Material is issued against a requisition and reported manually.
-3: Material is issued automatically based on the quantity reported as put away. The issue is always made from the location entered per item/warehouse.
-4: Material is issued automatically based on the quantity reported as produced in the operation where it is used. The issue is always made from the location entered per item/warehouse.
-5: Material is issued automatically based on the quantity reported as put away. The issue is made from the location entered in the work center for the operation to which the material is connected.
-6: Material is issued automatically based on the quantity that is reported as produced in the operation where it is used. The issue is made from the location specified in the work center for the operation to which the material is connected.
-7: The system sets this option to exclude the issue of the bulk item for child process orders or pack orders in (PMS060).
-8: Material is reported on one manufacturing order and issued to the next order by an external manufacturing execution system.
-9: Material is issued automatically by an external manufacturing execution system.
-0: Material issue method 0 may be used for non-stocked items for work orders in (MOS101). The material transaction status is set to 90 as soon as the transaction is finished.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Physical inventory cycle
-The field indicates the applicable physical inventory cycle.
-The inventory cycle contains information as to how many days are to elapse before inventory for the item is once again taken.
-</t>
-      </text>
-    </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">Planner
 The field indicates the person responsible for acquisition of each item respectively per warehouse. Planned orders and shortage analyses are sorted and processed per planner.
 The default is the person specified as responsible for item in (MMS001).
-</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Buyer
-The field indicates the buyer normally responsible for purchasing.
-The buyer can, for example, be responsible for purchase orders, agreements, item/supplier combinations or item/warehouse combinations.
-The specified buyer for each item/warehouse is copied to the planned orders generated by M3.
 </t>
       </text>
     </comment>
@@ -568,426 +250,12 @@
 </t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Warehouse type
-The field indicates group warehouses of the same type.
-In addition to being used as classification, the term also determines whether the warehouse balance should be accumulated by facility level.
-</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Warehouse subtype
-The field indicates the warehouse subtype, and is used to differentiate warehouses within each type.
-The field is defined in a separate table and is used for informational purposes only.
-</t>
-      </text>
-    </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">Location
 The field indicates the default location that is proposed upon receipt, issue etc.
 If storage method 1 (single location) is used, it is not possible to change this location.
 Even if storage method 2 or 3 is used, a standard location can be entered.
-</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Stock zone
-The field indicates the ID of a stock zone which is used to divide a warehouse into different areas.
-The stock zone is specified in three different programs, depending on the desired purpose:
-1. Stock zone per location (MMS010) is a central search key for making inquiries regarding locations, for example when searching for available locations (using (MMS010), system directed put-away or (MMS160)). Entering a stock zone in (MMS010) is mandatory.
-2. Stock zone per balance ID (MWS060) is automatically retrieved from the location when the balance ID is created and is used to split an order into several picking lists (one picking list per stock zone). The printers used to print the picking lists are defined per stock zone in (MMS040).
-3. Stock zone per item/warehouse (MMS002) is used to suggest locations when performing stock receipt. The stock zone entered here is also suggested as the From stock zone on proposed replenishment orders (MMS170).
-The stock zone in (MMS002) is entered manually and is not mandatory.
-</t>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Planning policy
-The field indicates the planning policy which contains a number of rules that determine how generation of planned orders, action messages and warning messages are to be applied.
-</t>
-      </text>
-    </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">ABC class - manual
-The field indicates an optional ABC class that is to be used to group item numbers per warehouse according to the definition per installation.
-</t>
-      </text>
-    </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">ABC class - volume
-The field indicates a code, usually A, B or C, used to group items according to how they affect the total sales volume (the sales volume is the product of an item's annual usage multiplied by a particular price).
-The ABC class is defined in the parameter file.
-ABC class sales volume can also be used as selection criteria when printing reports, taking inventory or determining stock control values.
-The sales volume is updated per warehouse/item, either automatically or manually depending upon the method you have chosen.
-</t>
-      </text>
-    </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">ABC method  - volume
-Select the check box to automatically update the ABC class for the item/warehouse combination. If you do not select the check box, the ABC class must be manually updated.
-</t>
-      </text>
-    </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">ABC class - frequency
-The field indicates the ABC class frequency code, which is a code from A to J.
-This code is used for two main purposes:
-The code can also be used as selection criteria.
-The code is based on one of the following (applies to 1 and 2 above):
-When the ABC class frequency is calculated automatically as in (MMS675), enter the division basis to be used.
-The ABC class frequency is updated for each item/warehouse. Depending on the ABC frequency method, this is done manually or automatically.
-</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">ABC method - frequency
-Select the check box to automatically update the ABC class for the item/warehouse combination. If you do not select the check box, the ABC class must be manually updated.
-</t>
-      </text>
-    </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">ABC class - contribution
-The field indicates group items based on their contribution margin for each item/warehouse.
-The value can be set manually or automatically. The valid values are A to J.
-When grouping is performed automatically, the contribution is calculated by multiplying the sales quantity by the contribution margin for each unit. The contribution margin is calculated by subtracting the item file's sales price or a price list price with the specified costing price.
-</t>
-      </text>
-    </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">ABC method - contribution
-Select the check box to automatically update the ABC class for the item/warehouse combination. If you do not select the check box, the ABC class must be manually updated.
-</t>
-      </text>
-    </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Safety stock
-The field indicates a buffer quantity which is only used during unexpected circumstances such as increased demand, difficulties in delivery, etc.
-The selected safety stock method determines how the safety stock is entered.
-</t>
-      </text>
-    </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
-      <text>
-        <t>Safety stock method
-The field indicates how the safety stock is calculated and updated.
-0: Manually
-1: Automatically according to the formula: Number of safety stock days * Daily usage
-2: Automatically according to the formula: Safety stock percentage * Lead time * Daily usage
-3: Automatically according to the formula: Safety factor * 1.25 * Mean absolute deviation (MAD) * Square root of lead time in number of periods
-4: Number of safety stock days in accordance with (MMS093)
-5: Number of average issues in accordance with the safety stock control table
-6: By integration to MerciaLincs
-7: Automatically according to Poisson table
-8: Automatically, average quantity/issue. Optionally multiplied with safety stock factor.</t>
-      </text>
-    </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Safety stock unit
-The field indicates the safety stock unit.
-Depending on the safety stock method used, the value is entered as:
-</t>
-      </text>
-    </comment>
-    <comment ref="AB1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Maximum stock
-The field indicates the maximum quantity that is allowed for each combination of warehouse and item.
-If the planned on-hand balance exceeds the maximum stock level an action message is issued.
-If the on-hand balance exceeds the maximum stock level a planning message is issued to so called planning mail box.
-</t>
-      </text>
-    </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum stock method
-The field indicates whether the maximum stock is to be calculated automatically.
-0: No
-1: Yes
-2: Yes, with maximum stock 0 (zero)</t>
-      </text>
-    </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Maximum stock percentage
-The field indicates calculation of the maximum inventory quantity according to maximum inventory method 1.
-The percentage entered in the field is multiplied by the sum of the reorder point and the order quantity.
-</t>
-      </text>
-    </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
-      <text>
-        <t>Order policy
-The field indicates the process for calculating the order quantity for each item/warehouse. The alternatives are described in more detail below.
-Fixed quantity/variable period:
-00: Manually entered quantity
-01: Fixed quantity calculated from run-out time
-02: Economic order quantity - Wilson's formula.
-11: Discrete order quantity
-12: Manually entered run-out time
-13: Economic run-out time
-15: Run-out time using a timetable (so-called point-of-time table).
-21: Least unit cost
-23: Period-based order quantity without balance check
-24: Period-based order quantity with balance check
-25: Up to maximum on-hand balance.</t>
-      </text>
-    </comment>
-    <comment ref="AF1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Order quantity days
-This field indicates the number of days demand that is to apply when calculating the order quantity in accordance with the rules which apply for each order quantity method.
-If nothing has been specified per item/warehouse combination, the number of days is obtained from the ABC sales volume class.
-</t>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
-      <text>
-        <t>Annual demand method
-The field indicates how the annual demand is updated.
-0: Manually
-1: Automatically, either integrated with the forecasting or based on the demand calculation results.</t>
-      </text>
-    </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Minimum order quantity
-The field indicates the minimum order quantity allowed.
-The information is used when batch size is calculated in connection with the requirements calculation, but only if it is greater than zero.
-The minimum order quantity can be specified in following locations and search hierarchy:
-1. Item/supplier (PPS040) in the PO unit of measure (U/M) in PPS040
-2. Item/warehouse (MMS002) in basic U/M
-Warning messages in PPS171, PPS201 and OIS145 display the minimum order quantity in the same U/M as entered on the order.
-</t>
-      </text>
-    </comment>
-    <comment ref="AI1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Maximum order quantity
-The field indicates maximum order quantity, which is the maximum allowed order quantity for each combination of item/warehouse.
-The information is used at calculation of batch size in connection with requirement calculation, only if the batch size is greater than zero.
-</t>
-      </text>
-    </comment>
-    <comment ref="AJ1" authorId="0" shapeId="0">
-      <text>
-        <t>Acquisition code
-The field indicates how acquisition is performed for requirements (immediate or planned) for each item/warehouse.
-1: Manufacturing
-2: Purchasing
-3: Distribution from another warehouse
-6: Maintenance.</t>
-      </text>
-    </comment>
-    <comment ref="AK1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Forecast method
-The field indicates the ID of a forecast method. Forecast methods define how the item is processed during forecasting and are created in (FCS300).
-</t>
-      </text>
-    </comment>
-    <comment ref="AL1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Forecast logic
-The field indicates how the forecast should be managed when transferred to material requirements planning. The parameters defined for each forecast logic mainly determine how reservations should be matched against forecasts.
-Forecast calculation methods are defined in (FCS305).
-</t>
-      </text>
-    </comment>
-    <comment ref="AM1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Planning time fence
-The field indicates the planning time fence which is a time in the planning horizon of the master scheduling process that marks a limit. Inside the planning time fence changes to the material plan are reviewed by the responsible planner. Planned orders beyond the planning time fence can be changed using system planning logic.
-</t>
-      </text>
-    </comment>
-    <comment ref="AN1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Supply lead time
-The field indicates the supply lead time in days.
-For manufactured items (acquisition method 1) and distribution items (acquisition method 3), the lead time is always expressed in workdays.
-For manufactured items, the supply lead time is updated automatically (from the product header). It always includes the directly ordered acquisition of included material, regardless of whether the material is manufactured or purchased.
-For purchased items (acquisition method 2), you can set the supply lead time to either five or seven days per week using setting 33 in (CRS780).
-For purchased items, this field is updated manually in (MMS002) or for the main supplier in (PPS044). (PPS044) is reached via option 14 in (PPS040). When one program is updated, the other is updated automatically if the main supplier is the same and single supply has been selected in the multiple supply field in (MMS002). This field is also updated when a new purchase agreement becomes valid (order date) during a separate user-initiated run (PPS950).
-For distributed items, this lead time reflects the supply chain lead time if the item is order initiated for the supplying warehouse or for the supplying and the receiving warehouse. Example: An item is order initiated at warehouse 100 (supplying warehouse) where the total lead time is 20 days. At warehouse 200 (receiving warehouse), the transport lead time is 2 days. The total lead time at warehouse 200 will then be 20 (supply lead time) + 2 (transport lead time) = 22 days. Note, no automatic update of the lead time value for the item on the receiving warehouse is performed if changing the item on the supplying warehouse from order initiated to MRP, this has to be done manually.
-</t>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Inspection lead time
-The field indicates the time normally required for goods receipt, quality inspection, and put-away. Inspection lead time is not allowed for direct put-away where the inspection point is defined as 1 on (PPS345/E).
-The inspection lead time is mainly used for purchased items and is thus always entered via the current goods receiving method.
-In order for a changed inspection lead time to affect all appropriate items, (MMS987) should be run.
-When a manufactured product is quality-inspected, the inspection lead time is used; otherwise it is not used. In this case it is entered immediately for the item/warehouse combination.
-Items procured through distribution orders do not use inspection lead time.
-</t>
-      </text>
-    </comment>
-    <comment ref="AP1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Transportation lead time
-The field indicates transportation lead time, which is always maintained through other associated files depending on the method of procurement.
-When a need is fulfilled via a distribution order, the transportation time is obtained from the respective warehouse relation (DPS001). If there are several supplying warehouses, the transportation time from the warehouse which comes first in alphabetical order is used.
-For purchased items, any transportation time is obtained from the file which is maintained in (PPS010). The elements making up this time for purchased items are clearly explained in the function.
-The transportation lead time is not used for manufactured items.
-</t>
-      </text>
-    </comment>
-    <comment ref="AQ1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Order multiple
-The field indicates the order multiple quantity. It is used in order to avoid the need to break up packages, for example.
-The order multiple can be specified in following locations and search hierarchy:
-1. Item/supplier (PPS040) in the PO U/M in PPS040
-2. Alternative U/M (MMS015) in the alternate U/M
-3. Item/warehouse (MMS002) in the basic U/M
-When an order is planned or created, a check is made to ensure that the order quantity is divisible by the order multiple.
-The order multiple is also used when the order quantity is calculated during the material requirements calculation (MRP).
-Warning messages in PPS171, PPS201 and OIS145 display the order multiple in the same U/M as entered on the order.
-</t>
-      </text>
-    </comment>
-    <comment ref="AR1" authorId="0" shapeId="0">
-      <text>
-        <t>Multiple supply
-The field indicates what kind of supply that is to be connected to the item.
-1: Single supply only from the supplier or warehouse set for the item. No override accepted.
-2: Multiple supply, the supplier or warehouse set for the item is defaulted. If a valid agreement for the main supplier is not found, the next supplier with a valid agreement will be chosen. The value can be overridden.
-3: Different warehouses according to a percentage set in the distribution relationship table for distribution orders.
-4: Multiple supply, the required quantity supplied according to different supply methods - valid supply methods and percentages are set in (RPS090).</t>
-      </text>
-    </comment>
-    <comment ref="AS1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Planning horizon
-The field indicates the planning horizon, which is specified for each item/warehouse, and indicates how many days that are covered by the requirements planning from the current system date.
-There may well be requirements beyond the date fixed by the planning horizon, but these are not considered when orders are generated. There is no reason to use a longer horizon in requirements planning than what is required in order to plan the item with the longest lead time.
-To support long-term planning, it is possible to specify a long-term planning horizon per planning policy in (MMS037).
-It is also possible to override the planning horizon for each simulated version of the requirements planning, but the overriding horizon is then used for all items.
-</t>
-      </text>
-    </comment>
-    <comment ref="AT1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Order type
-The field indicates an order type which is a combined ID for settings that determine how the order is processed during order entry and in the processing flow.
-Order types are defined per order category in the following programs:
-</t>
-      </text>
-    </comment>
-    <comment ref="AU1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Safety time
-The field indicates how many days before the actual need date a planned order should be available in stock. The purpose is to protect the scheduling from any fluctuations in the item's delivery time. This information is only used when planning method 1 or 3 are applied.
-</t>
-      </text>
-    </comment>
-    <comment ref="AV1" authorId="0" shapeId="0">
-      <text>
-        <t>Planning method
-The field indicates the material planning method set for the item/warehouse during acquisition order entry. There are two basic methods (material requirements planning and reorder point planning) used to plan and create acquisition orders.
-0: Manually planned
-1: Material requirements planning (MRP)
-2: Reorder point planning (ROP) per item/warehouse
-3: Order-driven - Acquisition orders are only triggered, created and released by a requiring order
-4: Reorder point planning (ROP) per item and facility
-5: Reorder point planning (ROP) per item and global facility.</t>
-      </text>
-    </comment>
-    <comment ref="AW1" authorId="0" shapeId="0">
-      <text>
-        <t>Master scheduled
-The field indicates whether the item is part of the master schedule. The master schedule represents what the company plans to produce expressed in specific configurations, quantities and dates. The master schedule takes into account the forecast, the production plan and other important considerations such as backlog, availability of material and capacity, management policies and goals.
-0: Not a master scheduled item
-1: Master scheduled item - may be used for manufactured, purchased or distributed items. By selecting this option, planned orders will not automatically be scheduled inside the planning time fence. The system will instead apply an A3 action message to the planned order and place it on the planning time fence with an alternative date.
-2: Master scheduled item that always contains a customer order-specific configuration - may be used for scheduling of products that display a relatively low item volume, are very specialized to customer needs, and generate high inventory costs.
-3: Planning entity - used for forecasting on a more aggregated level. For instance, pasta could be an appropriate item to forecast when selling macaroni and spaghetti. If pasta is the planning entity, the forecast on pasta will be consumed when macaroni or spaghetti is sold. The planning entity should have inventory accounting = 2. The connection between the items that you sell and the planning entity is defined in (RPS045).
-4: Process planning item - used for items to be defined as process planned and whose inventory accounting code in (MMS001) must equal 2. For end items connected to a planning process the master schedule code should be 0 or 1.</t>
-      </text>
-    </comment>
-    <comment ref="AX1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Inspection location
-The field indicates the location where goods received are stored while waiting to be quality inspected in the purchase component group.
-If the item is to be inspected, this location is proposed by default in (PPS300). If the location is blank per item/warehouse, the location is proposed by default from the goods receiving method.
-</t>
-      </text>
-    </comment>
-    <comment ref="AY1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Facility
-The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).
-</t>
-      </text>
-    </comment>
-    <comment ref="AZ1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Division
-The field indicates a division. This is an identity for a legal unit within a company group.
-Division is a key value in the financial system in M3.
-One division may consist of several facilities. Facilities are used in material and production management and for purchasing purposes.
-</t>
-      </text>
-    </comment>
-    <comment ref="BA1" authorId="0" shapeId="0">
-      <text>
-        <t>History storage method
-The field indicates if and how stock transactions are stored in the stock transaction history file.
-1: Detailed storage.
-2: Accumulated storage on daily level per order and transaction type.
-3: Accumulated storage on daily level per transaction type.</t>
-      </text>
-    </comment>
-    <comment ref="BB1" authorId="0" shapeId="0">
-      <text>
-        <t>Status
-The field indicates the status of the record. Usually the status is entered as follows:
-10: Preliminary
-20: Definite
-90: Blocked/expired.</t>
-      </text>
-    </comment>
-    <comment ref="BC1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">CTP policy
-The field indicates the CTP policy to use. The CTP policy determines how the ATP and CTP calculations are done.
-</t>
-      </text>
-    </comment>
-    <comment ref="BD1" authorId="0" shapeId="0">
-      <text>
-        <t>Returnable/non-returnable indicator
-The field is a value that indicates whether an item is considered returnable.
-This field is mainly used for purchased items. However, since the indicator is also contained in the item master it can influence different acquisition types.
-0: The item is fully returnable.
-1: The item is returnable with restrictions. Only for information; no warnings are issued.
-2: The item is not returnable to the supplier. You can receive warning messages at customer order entry and customer order return when manually adding a material line on a work order, when entering a planned purchase order, and when entering a purchase order line. You can also receive warning message 65 on the planned purchase order to avoid an auto release.
-3: The item is not returnable to us and/or the supplier. Same as alternative 2, except that the customer order return and work order return can be blocked for this item.</t>
-      </text>
-    </comment>
-    <comment ref="BE1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Supply chain policy
-The field identifies the supply chain policy.
-The supply chain policy determines whether to include the item in the supply chain link function.
-If you add a supply chain policy to an item, then this item will be included in the supply chain function and get planned orders automatically generated according to the demand from the above level. The demand and the generated planned order will be preallocated and assigned a supply chain number. Thus, it is possible to have full traceability between demand and supply. Note that currently the start of a supply chain can only be done via a customer order or a released distribution order, and the generated planned orders are always lot sized according to lot-for-lot. It is however possible to manually preallocate lot sized planned purchase orders to one or more supply chains afterwards. Thereby you have the possibility to plan the purchase orders separately from the rest of the supply chain, for example via MRP.
 </t>
       </text>
     </comment>
@@ -1003,121 +271,9 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve">Company
-The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.
-</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Facility
-The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).
-</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
         <t xml:space="preserve">Item number
 The field indicates the item number (for Maintenance, the item number or equipment number), which is a unique ID for an individual item.
 Items are entered and maintained in (MMS001). Item number can consist up to 15 alphanumeric characters.
-</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Administrative lead time
-The field indicates the administrative lead time, which is entered for each item and facility. The administrative lead time is added to the total lead time for each item and warehouse. The administrative lead time is only applicable for acquisition methods 1, 2 and 3.
-In principle the administrative lead time can be considered as the time allotted to perform activities that are required before a planned order can be released. For example, a quotation inquiry.
-</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Customs statistical number
-The field indicates the customs statistics number, which is specified for each item/facility. It is used in printouts of various shipping documents, such as the unit document. It is also used for regulating and calculating data for transactions to INTRASTAT, the trade statistics of the EU.
-</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Country of origin
-The field indicates the itemâs country of origin. It is retrieved from (MMS003).
-For Intrastat transactions split per country of origin of the lot number, as set in (CRS726), the field is instead updated from (MMS235).
-The information can be used for trade statistics reported to the authorities.
-</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Costing model
-The field indicates the ID of the costing model used for each item.
-Costing models are defined in (PPS285).
-</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Costing model - product costing
-The field indicates the ID of the product costing model.
-The costing model is defined in (PCS025).
-For manufacturing the costing model is generally applied in (PCS001), or in (MMS003) for item per facility.
-For maintenance the costing model is generally applied in (CRS788), parameter 21, or in (MOS301/F) for service per facility.
-</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Costing model - sales price
-The field indicates the ID of a costing model for sales prices.
-Costing models can be connected to different price lists and are used to calculate both basic prices and order-costed prices. It is also used for price origin C (price is calculated online at CO line entry).
-</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Calculate price for line type 0
-The field indicates whether the sales price on a customer order line with line type 0 is calculated (dynamically) during customer order entry.
-Select the check box if line type 0 should be calculated (dynamically) during customer order entry.
-</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Costing decimal places
-The field indicates the number of decimal places (up to four) that will be shown for the item cost.
-</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Inventory accounting method
-The field indicates the inventory accounting method that defines how the cost of an item is determined per item/facility.
-0: Zero cost
-1: Standard cost
-2: Average cost
-3: Dynamic product cost
-4: Actual cost
-5: Simplified purchasing
-6: FIFO cost</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">General distribution costing model
-The field indicates the general costing model to apply during distribution costing if there is no costing model selected for each combination of item and facility in (MMS003/F).
-The costing model can be overruled when calculating the cost in (PCS280).
-</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Alternate structure
-Select this check box to activate the use of alternate product structures (i.e. alternate manufacturing processes) for this item-facility setup.
-If this setting is enabled, you may create alternate structures for the item in (PDS023).
 </t>
       </text>
     </comment>
@@ -1139,58 +295,6 @@
 </t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">UN number
-The field indicates the identity/number of the item in question in the summary of the most common transported goods, prepared by the UN experts commission.
-The UN number is used for identification of transport documents.
-</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">UN pack code
-The field indicates the packaging class that applies to the item according to UN regulations.
-The possible values are I, II, III.
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>System</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Item number
-The field indicates the item number (for Maintenance, the item number or equipment number), which is a unique ID for an individual item.
-Items are entered and maintained in (MMS001). Item number can consist up to 15 alphanumeric characters.
-</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Purchase price
-The field indicates the purchase price.
-The price information is affected by the purchase price quantity, purchase price U/M, currency and discount. All factors must be considered to understand purchase price correctly.
-The price is retrieved from the agreement line or the item/supplier record and displayed by default on the purchase order line. The default price is the price which has the latest From date. If an agreement price exists, it is not necessary to enter a price in (PPS040) or (MMS001).
-If no price exists in the agreement or in (PPS040), then (MMS001) is checked for a purchase price.
-If no agreement price exists, the agreement is handled as inactive.
-</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Purchase price quantity
-The field indicates the purchase price per item when purchased in a specific quantity.
-</t>
-      </text>
-    </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">Currency
@@ -1204,39 +308,6 @@
 The field indicates the sales price for each sales price unit and price quantity.
 Sales price is used during automatic pricing of customer order lines when agreed prices or price lists are not available.
 </t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Currency - sales price
-The field indicates the currency in which the sales price (according to the item file) has been entered.
-</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Order total discount generating
-The field indicates if the item value of a customer order line is included in the basis of a total order discount.
-"Yes" indicates that the item value of the order line is included in the amount used to find a quantity-dependent percentage discount. All order lines will be charged with the order total discount that applies for the order.
-</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>Bonus generating
-The field indicates if and how the item (in other words, the customer order line) affects a bonus agreement (agreement type 9).
-0: Does not affect agreement.
-1: Generating.
-2: Generating and paying.</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Commission generating
-The field indicates if and how the item (customer order line) affects a commission agreement (agreement types 1-8, commission agreement).
-0: Does not affect commission agreement.
-1: Generating.
-2: Generating and paying.</t>
       </text>
     </comment>
   </commentList>
@@ -3986,7 +3057,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
